--- a/account_employee_setup/positive_imports/employee_full.xlsx
+++ b/account_employee_setup/positive_imports/employee_full.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/henrycole/Desktop/account_employee_setup/positive_imports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/henrycole/Desktop/automation/hr_regression/account_employee_setup/positive_imports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB85D0CD-9DEA-3F4D-ACE5-C76D928AF97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CB31F1-60D4-4A4C-B232-89D91850B274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32160" yWindow="3060" windowWidth="24520" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="19820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="employee_template" sheetId="1" r:id="rId1"/>
@@ -950,42 +950,27 @@
     <t>Contractor</t>
   </si>
   <si>
-    <t>employee@hr_regression.com</t>
-  </si>
-  <si>
     <t>User</t>
   </si>
   <si>
     <t>25/06/2021</t>
   </si>
   <si>
-    <t>line@hr_regression.com</t>
-  </si>
-  <si>
     <t>Line Manager</t>
   </si>
   <si>
     <t>15/12/2015</t>
   </si>
   <si>
-    <t>finance@hr_regression.com</t>
-  </si>
-  <si>
     <t>Finance User</t>
   </si>
   <si>
     <t>09/01/2018</t>
   </si>
   <si>
-    <t>contractor@hr_regression.com</t>
-  </si>
-  <si>
     <t>22/03/2019</t>
   </si>
   <si>
-    <t>volunteer@hr_regression.com</t>
-  </si>
-  <si>
     <t>02/01/2022</t>
   </si>
   <si>
@@ -1194,6 +1179,21 @@
   </si>
   <si>
     <t>VU</t>
+  </si>
+  <si>
+    <t>employee@hr-regression.com</t>
+  </si>
+  <si>
+    <t>line@hr-regression.com</t>
+  </si>
+  <si>
+    <t>finance@hr-regression.com</t>
+  </si>
+  <si>
+    <t>contractor@hr-regression.com</t>
+  </si>
+  <si>
+    <t>volunteer@hr-regression.com</t>
   </si>
 </sst>
 </file>
@@ -1765,28 +1765,28 @@
     </row>
     <row r="2" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>309</v>
+        <v>386</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>306</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>45</v>
@@ -1795,7 +1795,7 @@
         <v>73</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>74</v>
@@ -1807,78 +1807,78 @@
         <v>286</v>
       </c>
       <c r="S2" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="T2" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="Z2" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="AJ2" s="2" t="s">
         <v>303</v>
       </c>
       <c r="AK2" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="AL2" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="AO2" s="2" t="s">
-        <v>382</v>
-      </c>
       <c r="AQ2" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>306</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>48</v>
@@ -1887,7 +1887,7 @@
         <v>73</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>88</v>
@@ -1899,78 +1899,78 @@
         <v>284</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="T3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="W3" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="Z3" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="X3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>303</v>
       </c>
       <c r="AK3" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="AL3" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="AL3" s="2" t="s">
+      <c r="AM3" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AN3" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="AN3" s="2" t="s">
+      <c r="AO3" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="AO3" s="2" t="s">
-        <v>383</v>
-      </c>
       <c r="AQ3" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>315</v>
+        <v>388</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>306</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>49</v>
@@ -1979,7 +1979,7 @@
         <v>72</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>131</v>
@@ -1991,78 +1991,78 @@
         <v>285</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="T4" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="W4" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="X4" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="Z4" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="V4" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="W4" s="2" t="s">
+      <c r="AA4" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="AJ4" s="2" t="s">
         <v>303</v>
       </c>
       <c r="AK4" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="AL4" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="AL4" s="2" t="s">
-        <v>369</v>
-      </c>
       <c r="AM4" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="AO4" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AQ4" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>318</v>
+        <v>389</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>308</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>308</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>330</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>43</v>
@@ -2071,7 +2071,7 @@
         <v>72</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>161</v>
@@ -2083,84 +2083,84 @@
         <v>288</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="T5" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="X5" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="Y5" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="Z5" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="V5" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="Y5" s="2" t="s">
+      <c r="AA5" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="AJ5" s="2" t="s">
         <v>304</v>
       </c>
       <c r="AK5" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="AL5" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="AL5" s="2" t="s">
-        <v>370</v>
-      </c>
       <c r="AM5" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AN5" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AO5" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="AQ5" s="2" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>320</v>
+        <v>390</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>307</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>307</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>331</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>73</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>208</v>
@@ -2172,52 +2172,52 @@
         <v>289</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="T6" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y6" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="Z6" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="V6" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="X6" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="Y6" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="Z6" s="2" t="s">
+      <c r="AA6" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="AA6" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="AJ6" s="2" t="s">
         <v>305</v>
       </c>
       <c r="AK6" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="AL6" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="AL6" s="2" t="s">
+      <c r="AM6" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="AM6" s="2" t="s">
+      <c r="AN6" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="AN6" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="AO6" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="AQ6" s="2" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
